--- a/TestCases/TC02_CDS_phs001713_SampleTumorStatus-Normal_SampleType-DNA.xlsx
+++ b/TestCases/TC02_CDS_phs001713_SampleTumorStatus-Normal_SampleType-DNA.xlsx
@@ -542,10 +542,6 @@
           <t>dismiss_popup</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Dismiss warning popup</t>
@@ -571,8 +567,6 @@
           <t>CDS_Data-Btn</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Click Data nav button</t>
@@ -598,8 +592,6 @@
           <t>Data_page/Filter/StudyFacet/PHS_Accession/PHS_Accession_Ddn</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Expand phs filter</t>
@@ -625,7 +617,6 @@
           <t>Data_page/Filter/StudyFacet/PHS_Accession/phs001713_Chkbx</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>phs=phs001713</t>
@@ -656,8 +647,6 @@
           <t>Data_page/Filter/SamplesFacet/SampleTumorStatus/SampleTumorStatus-Ddn</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Expand tumor_status filter</t>
@@ -680,10 +669,9 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Data_page/Filter/SamplesFacet/SampleTumorStatus/Normal-Chkbx</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Data_page/Filter/SamplesFacet/SampleTumorStatus/Normal_Chkbx</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>tumor_status=Normal</t>
@@ -714,8 +702,6 @@
           <t>Data_page/Filter/SamplesFacet/SampleType/SampleType-Ddn</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Expand sample_type filter</t>
@@ -741,7 +727,6 @@
           <t>Data_page/Filter/SamplesFacet/SampleType/DNA-Chkbx</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>sample_type=DNA</t>
@@ -762,14 +747,11 @@
           <t>read_stat_bar</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>CDS</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Read stat bar counts</t>
@@ -785,14 +767,11 @@
           <t>multi_function</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>ParticipantsTab</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Compare ParticipantsTab</t>
@@ -808,14 +787,11 @@
           <t>multi_function</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>SamplesTab</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Compare SamplesTab</t>
@@ -831,14 +807,11 @@
           <t>multi_function</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>FilesTab</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Compare FilesTab</t>

--- a/TestCases/TC02_CDS_phs001713_SampleTumorStatus-Normal_SampleType-DNA.xlsx
+++ b/TestCases/TC02_CDS_phs001713_SampleTumorStatus-Normal_SampleType-DNA.xlsx
@@ -724,7 +724,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Data_page/Filter/SamplesFacet/SampleType/DNA-Chkbx</t>
+          <t>Data_page/Filter/SamplesFacet/SampleType/DNA_Chkbx</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
